--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-15 13:01:00</t>
+          <t>Timestamp: 2026-07-15 13:31:00</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7475</v>
+        <v>7715</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>7419</v>
+        <v>7479</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>30845</v>
+        <v>30905</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>44260</v>
+        <v>44320</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>53230</v>
+        <v>53290</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>23621</v>
+        <v>23681</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="2026-07-15" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2026-07-16" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-07-17" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2190,4 +2191,883 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-17 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>4627</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+4627</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>5492</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+3604</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>4382</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+925</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>483</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+1900</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>6525</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+1215</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>704</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+704</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>11480</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+1713</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>5640</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>5483</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>12183</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+2184</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+90</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>4342</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>6199</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+1420</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>27142</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1150</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>36398</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2905</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+80</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>40591</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2763</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>11079</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+2811</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>22445</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>831</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Lovebird | Gorelax</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>34994</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>49786</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+2658</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>16602</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>17125</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>19068</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>57552</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2517</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>907</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>28256</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1917</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>421</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+271</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4352</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -3097,7 +3097,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-18 13:01:00</t>
+          <t>Timestamp: 2026-07-18 13:31:00</t>
         </is>
       </c>
     </row>
@@ -3455,11 +3455,11 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>1890</v>
+        <v>2010</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>+1530</t>
+          <t>+1650</t>
         </is>
       </c>
     </row>
@@ -3530,11 +3530,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>40651</v>
+        <v>40771</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+4253</t>
+          <t>+4373</t>
         </is>
       </c>
     </row>
@@ -3575,11 +3575,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>43354</v>
+        <v>43474</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+2703</t>
+          <t>+2823</t>
         </is>
       </c>
     </row>
@@ -3635,11 +3635,11 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>22755</v>
+        <v>22875</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>+310</t>
+          <t>+430</t>
         </is>
       </c>
     </row>
@@ -3680,11 +3680,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>2793</v>
+        <v>2913</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+1962</t>
+          <t>+2082</t>
         </is>
       </c>
     </row>
@@ -3755,11 +3755,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>37489</v>
+        <v>37550</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+2495</t>
+          <t>+2556</t>
         </is>
       </c>
     </row>
@@ -3770,11 +3770,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>52351</v>
+        <v>52511</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+2505</t>
+          <t>+2665</t>
         </is>
       </c>
     </row>
@@ -3785,11 +3785,11 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>16902</v>
+        <v>17022</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>+300</t>
+          <t>+420</t>
         </is>
       </c>
     </row>
@@ -3830,11 +3830,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>60423</v>
+        <v>60543</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+2811</t>
+          <t>+2931</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -6617,7 +6617,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-22 13:01:00</t>
+          <t>Timestamp: 2026-07-22 13:31:00</t>
         </is>
       </c>
     </row>
@@ -7035,11 +7035,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>8162</v>
+        <v>8222</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+1692</t>
+          <t>+1752</t>
         </is>
       </c>
     </row>
@@ -7050,11 +7050,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>10120</v>
+        <v>10240</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+2559</t>
+          <t>+2679</t>
         </is>
       </c>
     </row>
@@ -7350,11 +7350,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>8312</v>
+        <v>8372</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+2635</t>
+          <t>+2695</t>
         </is>
       </c>
     </row>
